--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Premshankar Mishra\Git\TP\Selenium\April_8\8_April\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Premshankar Mishra\Git\TP\Selenium\WorkShopDemo\WorkShopDemo\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5865884C-9674-48B3-918C-3320852F366B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" tabRatio="500" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="151">
   <si>
     <t>TC_ID</t>
   </si>
@@ -469,37 +469,31 @@
     <t>orderDetails</t>
   </si>
   <si>
-    <t>2267247</t>
-  </si>
-  <si>
-    <t>2267248</t>
-  </si>
-  <si>
     <t>Order number:</t>
   </si>
   <si>
-    <t>2267256</t>
-  </si>
-  <si>
-    <t>2267257</t>
-  </si>
-  <si>
-    <t>2267258</t>
-  </si>
-  <si>
-    <t>2267259</t>
-  </si>
-  <si>
-    <t>2267260</t>
-  </si>
-  <si>
-    <t>2267261</t>
-  </si>
-  <si>
-    <t>2267374</t>
-  </si>
-  <si>
-    <t>2267375</t>
+    <t>2267456</t>
+  </si>
+  <si>
+    <t>2267457</t>
+  </si>
+  <si>
+    <t>2267458</t>
+  </si>
+  <si>
+    <t>2267459</t>
+  </si>
+  <si>
+    <t>2267462</t>
+  </si>
+  <si>
+    <t>2267463</t>
+  </si>
+  <si>
+    <t>2267466</t>
+  </si>
+  <si>
+    <t>2267467</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1192,7 @@
         <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2082,10 +2076,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="155">
   <si>
     <t>TC_ID</t>
   </si>
@@ -494,6 +494,18 @@
   </si>
   <si>
     <t>2267467</t>
+  </si>
+  <si>
+    <t>2267484</t>
+  </si>
+  <si>
+    <t>2267485</t>
+  </si>
+  <si>
+    <t>2267487</t>
+  </si>
+  <si>
+    <t>2267488</t>
   </si>
 </sst>
 </file>
@@ -2076,10 +2088,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="157">
   <si>
     <t>TC_ID</t>
   </si>
@@ -506,6 +506,12 @@
   </si>
   <si>
     <t>2267488</t>
+  </si>
+  <si>
+    <t>2267493</t>
+  </si>
+  <si>
+    <t>2267494</t>
   </si>
 </sst>
 </file>
@@ -2088,10 +2094,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="162">
   <si>
     <t>TC_ID</t>
   </si>
@@ -512,6 +512,21 @@
   </si>
   <si>
     <t>2267494</t>
+  </si>
+  <si>
+    <t>2267505</t>
+  </si>
+  <si>
+    <t>2267506</t>
+  </si>
+  <si>
+    <t>2267517</t>
+  </si>
+  <si>
+    <t>2267518</t>
+  </si>
+  <si>
+    <t>2267519</t>
   </si>
 </sst>
 </file>
@@ -2094,10 +2109,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="170">
   <si>
     <t>TC_ID</t>
   </si>
@@ -527,6 +527,30 @@
   </si>
   <si>
     <t>2267519</t>
+  </si>
+  <si>
+    <t>2267530</t>
+  </si>
+  <si>
+    <t>2267531</t>
+  </si>
+  <si>
+    <t>2267533</t>
+  </si>
+  <si>
+    <t>2267534</t>
+  </si>
+  <si>
+    <t>2267536</t>
+  </si>
+  <si>
+    <t>2267537</t>
+  </si>
+  <si>
+    <t>2267540</t>
+  </si>
+  <si>
+    <t>2267541</t>
   </si>
 </sst>
 </file>
@@ -2109,10 +2133,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="178">
   <si>
     <t>TC_ID</t>
   </si>
@@ -551,6 +551,30 @@
   </si>
   <si>
     <t>2267541</t>
+  </si>
+  <si>
+    <t>2267577</t>
+  </si>
+  <si>
+    <t>2267579</t>
+  </si>
+  <si>
+    <t>2267582</t>
+  </si>
+  <si>
+    <t>2267584</t>
+  </si>
+  <si>
+    <t>2267585</t>
+  </si>
+  <si>
+    <t>2267591</t>
+  </si>
+  <si>
+    <t>2267592</t>
+  </si>
+  <si>
+    <t>2267596</t>
   </si>
 </sst>
 </file>
@@ -2133,10 +2157,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="183">
   <si>
     <t>TC_ID</t>
   </si>
@@ -575,6 +575,21 @@
   </si>
   <si>
     <t>2267596</t>
+  </si>
+  <si>
+    <t>2267685</t>
+  </si>
+  <si>
+    <t>2267686</t>
+  </si>
+  <si>
+    <t>2267688</t>
+  </si>
+  <si>
+    <t>2267692</t>
+  </si>
+  <si>
+    <t>2267694</t>
   </si>
 </sst>
 </file>
@@ -2157,10 +2172,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="185">
   <si>
     <t>TC_ID</t>
   </si>
@@ -590,6 +590,12 @@
   </si>
   <si>
     <t>2267694</t>
+  </si>
+  <si>
+    <t>2267705</t>
+  </si>
+  <si>
+    <t>2267707</t>
   </si>
 </sst>
 </file>
@@ -2172,10 +2178,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="189">
   <si>
     <t>TC_ID</t>
   </si>
@@ -596,6 +596,18 @@
   </si>
   <si>
     <t>2267707</t>
+  </si>
+  <si>
+    <t>2267727</t>
+  </si>
+  <si>
+    <t>2267728</t>
+  </si>
+  <si>
+    <t>2267741</t>
+  </si>
+  <si>
+    <t>2267742</t>
   </si>
 </sst>
 </file>
@@ -2178,10 +2190,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="193">
   <si>
     <t>TC_ID</t>
   </si>
@@ -608,6 +608,18 @@
   </si>
   <si>
     <t>2267742</t>
+  </si>
+  <si>
+    <t>2267853</t>
+  </si>
+  <si>
+    <t>2267856</t>
+  </si>
+  <si>
+    <t>2267864</t>
+  </si>
+  <si>
+    <t>2267865</t>
   </si>
 </sst>
 </file>
@@ -2190,10 +2202,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="199">
   <si>
     <t>TC_ID</t>
   </si>
@@ -620,6 +620,24 @@
   </si>
   <si>
     <t>2267865</t>
+  </si>
+  <si>
+    <t>2267870</t>
+  </si>
+  <si>
+    <t>2267871</t>
+  </si>
+  <si>
+    <t>2268628</t>
+  </si>
+  <si>
+    <t>2268629</t>
+  </si>
+  <si>
+    <t>2268631</t>
+  </si>
+  <si>
+    <t>2268632</t>
   </si>
 </sst>
 </file>
@@ -2202,10 +2220,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="302">
   <si>
     <t>TC_ID</t>
   </si>
@@ -638,6 +638,315 @@
   </si>
   <si>
     <t>2268632</t>
+  </si>
+  <si>
+    <t>2268709</t>
+  </si>
+  <si>
+    <t>2268714</t>
+  </si>
+  <si>
+    <t>2269032</t>
+  </si>
+  <si>
+    <t>2269033</t>
+  </si>
+  <si>
+    <t>2269288</t>
+  </si>
+  <si>
+    <t>2269289</t>
+  </si>
+  <si>
+    <t>2269294</t>
+  </si>
+  <si>
+    <t>2269295</t>
+  </si>
+  <si>
+    <t>2269296</t>
+  </si>
+  <si>
+    <t>2269298</t>
+  </si>
+  <si>
+    <t>2269299</t>
+  </si>
+  <si>
+    <t>2269301</t>
+  </si>
+  <si>
+    <t>2269302</t>
+  </si>
+  <si>
+    <t>2269303</t>
+  </si>
+  <si>
+    <t>2269304</t>
+  </si>
+  <si>
+    <t>2269305</t>
+  </si>
+  <si>
+    <t>2269306</t>
+  </si>
+  <si>
+    <t>2269307</t>
+  </si>
+  <si>
+    <t>2269308</t>
+  </si>
+  <si>
+    <t>2269309</t>
+  </si>
+  <si>
+    <t>2269310</t>
+  </si>
+  <si>
+    <t>2269311</t>
+  </si>
+  <si>
+    <t>2269312</t>
+  </si>
+  <si>
+    <t>2269313</t>
+  </si>
+  <si>
+    <t>2269314</t>
+  </si>
+  <si>
+    <t>2269315</t>
+  </si>
+  <si>
+    <t>2269317</t>
+  </si>
+  <si>
+    <t>2269318</t>
+  </si>
+  <si>
+    <t>2269319</t>
+  </si>
+  <si>
+    <t>2269320</t>
+  </si>
+  <si>
+    <t>2269321</t>
+  </si>
+  <si>
+    <t>2269322</t>
+  </si>
+  <si>
+    <t>2269323</t>
+  </si>
+  <si>
+    <t>2269324</t>
+  </si>
+  <si>
+    <t>2269325</t>
+  </si>
+  <si>
+    <t>2269326</t>
+  </si>
+  <si>
+    <t>2269327</t>
+  </si>
+  <si>
+    <t>2269328</t>
+  </si>
+  <si>
+    <t>2269329</t>
+  </si>
+  <si>
+    <t>2269330</t>
+  </si>
+  <si>
+    <t>2269331</t>
+  </si>
+  <si>
+    <t>2269332</t>
+  </si>
+  <si>
+    <t>2269333</t>
+  </si>
+  <si>
+    <t>2269334</t>
+  </si>
+  <si>
+    <t>2269335</t>
+  </si>
+  <si>
+    <t>2269336</t>
+  </si>
+  <si>
+    <t>2269337</t>
+  </si>
+  <si>
+    <t>2269338</t>
+  </si>
+  <si>
+    <t>2269339</t>
+  </si>
+  <si>
+    <t>2269340</t>
+  </si>
+  <si>
+    <t>2269342</t>
+  </si>
+  <si>
+    <t>2269343</t>
+  </si>
+  <si>
+    <t>2269344</t>
+  </si>
+  <si>
+    <t>2269345</t>
+  </si>
+  <si>
+    <t>2269346</t>
+  </si>
+  <si>
+    <t>2269347</t>
+  </si>
+  <si>
+    <t>2269349</t>
+  </si>
+  <si>
+    <t>2269350</t>
+  </si>
+  <si>
+    <t>2269351</t>
+  </si>
+  <si>
+    <t>2269352</t>
+  </si>
+  <si>
+    <t>2269353</t>
+  </si>
+  <si>
+    <t>2269354</t>
+  </si>
+  <si>
+    <t>2269355</t>
+  </si>
+  <si>
+    <t>2269356</t>
+  </si>
+  <si>
+    <t>2269357</t>
+  </si>
+  <si>
+    <t>2269358</t>
+  </si>
+  <si>
+    <t>2269359</t>
+  </si>
+  <si>
+    <t>2269360</t>
+  </si>
+  <si>
+    <t>2269362</t>
+  </si>
+  <si>
+    <t>2269363</t>
+  </si>
+  <si>
+    <t>2269364</t>
+  </si>
+  <si>
+    <t>2269365</t>
+  </si>
+  <si>
+    <t>2269366</t>
+  </si>
+  <si>
+    <t>2269367</t>
+  </si>
+  <si>
+    <t>2269368</t>
+  </si>
+  <si>
+    <t>2269369</t>
+  </si>
+  <si>
+    <t>2269370</t>
+  </si>
+  <si>
+    <t>2269371</t>
+  </si>
+  <si>
+    <t>2269372</t>
+  </si>
+  <si>
+    <t>2269373</t>
+  </si>
+  <si>
+    <t>2269374</t>
+  </si>
+  <si>
+    <t>2269375</t>
+  </si>
+  <si>
+    <t>2269376</t>
+  </si>
+  <si>
+    <t>2269377</t>
+  </si>
+  <si>
+    <t>2269378</t>
+  </si>
+  <si>
+    <t>2269379</t>
+  </si>
+  <si>
+    <t>2269380</t>
+  </si>
+  <si>
+    <t>2269381</t>
+  </si>
+  <si>
+    <t>2269382</t>
+  </si>
+  <si>
+    <t>2269383</t>
+  </si>
+  <si>
+    <t>2269384</t>
+  </si>
+  <si>
+    <t>2269385</t>
+  </si>
+  <si>
+    <t>2269387</t>
+  </si>
+  <si>
+    <t>2269388</t>
+  </si>
+  <si>
+    <t>2269389</t>
+  </si>
+  <si>
+    <t>2269390</t>
+  </si>
+  <si>
+    <t>2269391</t>
+  </si>
+  <si>
+    <t>2269392</t>
+  </si>
+  <si>
+    <t>2269393</t>
+  </si>
+  <si>
+    <t>2269394</t>
+  </si>
+  <si>
+    <t>2269395</t>
+  </si>
+  <si>
+    <t>2269397</t>
+  </si>
+  <si>
+    <t>2269398</t>
   </si>
 </sst>
 </file>
@@ -2204,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB2A282-A29A-41DA-8800-4B5D2341DDC3}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:CQ2"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="2" customWidth="true" width="14.6640625" collapsed="true"/>
@@ -2220,10 +2529,289 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>300</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>301</v>
+      </c>
+      <c r="C2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J2" t="s">
+        <v>214</v>
+      </c>
+      <c r="K2" t="s">
+        <v>215</v>
+      </c>
+      <c r="L2" t="s">
+        <v>216</v>
+      </c>
+      <c r="M2" t="s">
+        <v>217</v>
+      </c>
+      <c r="N2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O2" t="s">
+        <v>219</v>
+      </c>
+      <c r="P2" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>221</v>
+      </c>
+      <c r="R2" t="s">
+        <v>222</v>
+      </c>
+      <c r="S2" t="s">
+        <v>223</v>
+      </c>
+      <c r="T2" t="s">
+        <v>224</v>
+      </c>
+      <c r="U2" t="s">
+        <v>225</v>
+      </c>
+      <c r="V2" t="s">
+        <v>226</v>
+      </c>
+      <c r="W2" t="s">
+        <v>227</v>
+      </c>
+      <c r="X2" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>229</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>232</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>233</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>234</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>236</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>237</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>238</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>239</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>241</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>242</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>244</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>245</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>246</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>247</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>248</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>249</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>250</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>251</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>252</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>253</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>255</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>256</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>257</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>258</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>259</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>260</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>261</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>262</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>263</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>264</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>265</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>267</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>268</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>269</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>270</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>271</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>272</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>273</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>274</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>275</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>276</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>277</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>278</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>279</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>281</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>282</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>283</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>284</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>285</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>286</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>287</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>288</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>289</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>290</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>291</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>292</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>293</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>294</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>295</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>296</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>298</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/WorkShopDemo/TestData/TestScriptData.xlsx
+++ b/WorkShopDemo/TestData/TestScriptData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="310">
   <si>
     <t>TC_ID</t>
   </si>
@@ -947,6 +947,30 @@
   </si>
   <si>
     <t>2269398</t>
+  </si>
+  <si>
+    <t>2269410</t>
+  </si>
+  <si>
+    <t>2269411</t>
+  </si>
+  <si>
+    <t>2270391</t>
+  </si>
+  <si>
+    <t>2270392</t>
+  </si>
+  <si>
+    <t>2270396</t>
+  </si>
+  <si>
+    <t>2270397</t>
+  </si>
+  <si>
+    <t>2270399</t>
+  </si>
+  <si>
+    <t>2270401</t>
   </si>
 </sst>
 </file>
@@ -2529,10 +2553,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C2" t="s">
         <v>207</v>
